--- a/diseases/d018/2020-2025.xlsx
+++ b/diseases/d018/2020-2025.xlsx
@@ -769,11 +769,11 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0479627710278635</v>
+        <v>0.04843780981786251</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1802,11 +1802,11 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02622525784272068</v>
+        <v>0.0264850012746792</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -2687,11 +2687,11 @@
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03036239744892528</v>
+        <v>0.03066311644902699</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -3572,11 +3572,11 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.03786534554831329</v>
+        <v>0.03824037617199672</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -4457,11 +4457,11 @@
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0481030130484128</v>
+        <v>0.04857944084072176</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -5490,11 +5490,11 @@
         <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0579199544868644</v>
+        <v>0.05849361244086905</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -6375,11 +6375,11 @@
         <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0.03527086816815107</v>
+        <v>0.03562020224910064</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -7408,11 +7408,11 @@
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>0.02194787621596677</v>
+        <v>0.02216525507747217</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -8293,11 +8293,11 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02243872328788936</v>
+        <v>0.02266096365747953</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9178,11 +9178,11 @@
         <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>0.04284393727781374</v>
+        <v>0.04326827748349999</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -10211,11 +10211,11 @@
         <v>14</v>
       </c>
       <c r="R66" t="n">
-        <v>0.125937334453279</v>
+        <v>0.1271846585276039</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -11096,11 +11096,11 @@
         <v>9</v>
       </c>
       <c r="R72" t="n">
-        <v>0.1023766750009952</v>
+        <v>0.1033906466872504</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11981,11 +11981,11 @@
         <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>0.03939885847079457</v>
+        <v>0.03978479399688518</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -13014,11 +13014,11 @@
         <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0.02558822658690394</v>
+        <v>0.02583887866345745</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13899,11 +13899,11 @@
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0.02972440567903362</v>
+        <v>0.03001557411864647</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14784,11 +14784,11 @@
         <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>0.03575341249129044</v>
+        <v>0.0361036386804474</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15817,11 +15817,11 @@
         <v>8</v>
       </c>
       <c r="R104" t="n">
-        <v>0.04802174030692932</v>
+        <v>0.04849214214922837</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16702,11 +16702,11 @@
         <v>5</v>
       </c>
       <c r="R110" t="n">
-        <v>0.05075582479155741</v>
+        <v>0.05125300863655671</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17587,11 +17587,11 @@
         <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0.03273890908516203</v>
+        <v>0.03305960639954694</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -18620,11 +18620,11 @@
         <v>2</v>
       </c>
       <c r="R123" t="n">
-        <v>0.01787670624564522</v>
+        <v>0.0180518193402237</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -19505,11 +19505,11 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0.02040047653914808</v>
+        <v>0.02060031148237293</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -20390,11 +20390,11 @@
         <v>5</v>
       </c>
       <c r="R135" t="n">
-        <v>0.04753100719430377</v>
+        <v>0.04799660201047713</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21423,11 +21423,11 @@
         <v>12</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1486220283951681</v>
+        <v>0.1500778705932323</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -22308,11 +22308,11 @@
         <v>26</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1683915623609405</v>
+        <v>0.1700410590400679</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -23341,11 +23341,11 @@
         <v>6</v>
       </c>
       <c r="R155" t="n">
-        <v>0.0548001119990796</v>
+        <v>0.05532140959801665</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -24226,11 +24226,11 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>0.02315497690101955</v>
+        <v>0.02337524349211971</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -25111,11 +25111,11 @@
         <v>2</v>
       </c>
       <c r="R167" t="n">
-        <v>0.02413730925439614</v>
+        <v>0.02436692048875509</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -25996,11 +25996,11 @@
         <v>2</v>
       </c>
       <c r="R173" t="n">
-        <v>0.02336547669102882</v>
+        <v>0.02358774570568443</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -27029,11 +27029,11 @@
         <v>4</v>
       </c>
       <c r="R180" t="n">
-        <v>0.03880212795837519</v>
+        <v>0.03917124136709758</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -27914,11 +27914,11 @@
         <v>6</v>
       </c>
       <c r="R186" t="n">
-        <v>0.03971429371508202</v>
+        <v>0.04009208429254471</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -28799,11 +28799,11 @@
         <v>3</v>
       </c>
       <c r="R192" t="n">
-        <v>0.02834730505458151</v>
+        <v>0.02861696476004958</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -29832,11 +29832,11 @@
         <v>1</v>
       </c>
       <c r="R199" t="n">
-        <v>0.01648915021739271</v>
+        <v>0.01664600672923676</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -30717,11 +30717,11 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>0.01438415231730003</v>
+        <v>0.01452098459358952</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -31750,11 +31750,11 @@
         <v>2</v>
       </c>
       <c r="R212" t="n">
-        <v>0.02806663866790249</v>
+        <v>0.02833362847529662</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -32635,11 +32635,11 @@
         <v>5</v>
       </c>
       <c r="R218" t="n">
-        <v>0.06279910401943181</v>
+        <v>0.06339649371347618</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -33520,11 +33520,11 @@
         <v>4</v>
       </c>
       <c r="R224" t="n">
-        <v>0.03592529749491519</v>
+        <v>0.03626704444837967</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -34553,11 +34553,11 @@
         <v>2</v>
       </c>
       <c r="R231" t="n">
-        <v>0.01525392228207085</v>
+        <v>0.01539367369668078</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -35438,11 +35438,11 @@
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.01897953463667801</v>
+        <v>0.01915341888527102</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -36323,11 +36323,11 @@
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>0.02319720900038423</v>
+        <v>0.02340973419310902</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -37356,11 +37356,11 @@
         <v>1</v>
       </c>
       <c r="R250" t="n">
-        <v>0.02143984468217331</v>
+        <v>0.02163626948150986</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -38241,11 +38241,11 @@
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.0280475345186464</v>
+        <v>0.02830449679712273</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -39126,11 +39126,11 @@
         <v>2</v>
       </c>
       <c r="R262" t="n">
-        <v>0.02565751904587954</v>
+        <v>0.02589258478934786</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -40159,11 +40159,11 @@
         <v>1</v>
       </c>
       <c r="R269" t="n">
-        <v>0.02418133301858235</v>
+        <v>0.02440287443160456</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
@@ -41044,11 +41044,11 @@
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>0.0168706974548249</v>
+        <v>0.01702526123135202</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
@@ -41929,11 +41929,11 @@
         <v>1</v>
       </c>
       <c r="R281" t="n">
-        <v>0.01391832540023054</v>
+        <v>0.01404584051586542</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -42962,11 +42962,11 @@
         <v>3</v>
       </c>
       <c r="R288" t="n">
-        <v>0.03085931742778388</v>
+        <v>0.0311420403356814</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -43847,11 +43847,11 @@
         <v>3</v>
       </c>
       <c r="R294" t="n">
-        <v>0.09278883600153694</v>
+        <v>0.09363893677243609</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -44732,11 +44732,11 @@
         <v>1</v>
       </c>
       <c r="R300" t="n">
-        <v>0.0788705106013064</v>
+        <v>0.07959309625657068</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -45765,11 +45765,11 @@
         <v>1</v>
       </c>
       <c r="R307" t="n">
-        <v>0.03600312403545997</v>
+        <v>0.03628539779021217</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO307" t="inlineStr">
@@ -46650,11 +46650,11 @@
         <v>0</v>
       </c>
       <c r="R313" t="n">
-        <v>0.01740268422066265</v>
+        <v>0.01753912574203994</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO313" t="inlineStr">
@@ -47535,11 +47535,11 @@
         <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>0.01648675347220672</v>
+        <v>0.01661601386087994</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO319" t="inlineStr">
@@ -48568,11 +48568,11 @@
         <v>1</v>
       </c>
       <c r="R326" t="n">
-        <v>0.02113686342590605</v>
+        <v>0.021302581872923</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO326" t="inlineStr">
@@ -49453,11 +49453,11 @@
         <v>2</v>
       </c>
       <c r="R332" t="n">
-        <v>0.02529377989966757</v>
+        <v>0.02549208964126452</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO332" t="inlineStr">
@@ -50486,11 +50486,11 @@
         <v>0</v>
       </c>
       <c r="R339" t="n">
-        <v>0.0305075395447244</v>
+        <v>0.0307467265032522</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO339" t="inlineStr">
@@ -51371,11 +51371,11 @@
         <v>1</v>
       </c>
       <c r="R345" t="n">
-        <v>0.02205279417436198</v>
+        <v>0.022225693754083</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
@@ -52256,11 +52256,11 @@
         <v>0</v>
       </c>
       <c r="R351" t="n">
-        <v>0.01423215470677674</v>
+        <v>0.01434373846110149</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO351" t="inlineStr">
@@ -53289,11 +53289,11 @@
         <v>1</v>
       </c>
       <c r="R358" t="n">
-        <v>0.01352759259257987</v>
+        <v>0.01363365239867072</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO358" t="inlineStr">
@@ -54174,11 +54174,11 @@
         <v>2</v>
       </c>
       <c r="R364" t="n">
-        <v>0.02635062307096287</v>
+        <v>0.02655721873491067</v>
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO364" t="inlineStr">
@@ -55059,11 +55059,11 @@
         <v>4</v>
       </c>
       <c r="R370" t="n">
-        <v>0.05474447627309666</v>
+        <v>0.05517368705087056</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO370" t="inlineStr">
@@ -56092,11 +56092,11 @@
         <v>0</v>
       </c>
       <c r="R377" t="n">
-        <v>0.04318965760026803</v>
+        <v>0.04352827562700599</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO377" t="inlineStr">
@@ -56977,11 +56977,11 @@
         <v>1</v>
       </c>
       <c r="R383" t="n">
-        <v>0.02125561967689461</v>
+        <v>0.0214251649595342</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO383" t="inlineStr">
@@ -58010,11 +58010,11 @@
         <v>0</v>
       </c>
       <c r="R390" t="n">
-        <v>0.01214606838679692</v>
+        <v>0.01224295140544811</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO390" t="inlineStr">
@@ -58895,11 +58895,11 @@
         <v>0</v>
       </c>
       <c r="R396" t="n">
-        <v>0.01617121895684009</v>
+        <v>0.01630020855725359</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO396" t="inlineStr">
@@ -59780,11 +59780,11 @@
         <v>0</v>
       </c>
       <c r="R402" t="n">
-        <v>0.01723046910685145</v>
+        <v>0.01736790780772872</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO402" t="inlineStr">
@@ -60665,11 +60665,11 @@
         <v>0</v>
       </c>
       <c r="R408" t="n">
-        <v>0.01892526934686962</v>
+        <v>0.01907622660848892</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO408" t="inlineStr">
@@ -61698,11 +61698,11 @@
         <v>1</v>
       </c>
       <c r="R415" t="n">
-        <v>0.02499830354026808</v>
+        <v>0.02519770231121297</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO415" t="inlineStr">
@@ -62583,11 +62583,11 @@
         <v>0</v>
       </c>
       <c r="R421" t="n">
-        <v>0.01447641871682191</v>
+        <v>0.01459188975649339</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO421" t="inlineStr">
@@ -63468,11 +63468,11 @@
         <v>0</v>
       </c>
       <c r="R427" t="n">
-        <v>0.008615234553425723</v>
+        <v>0.00868395390386436</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO427" t="inlineStr">
@@ -64501,11 +64501,11 @@
         <v>0</v>
       </c>
       <c r="R434" t="n">
-        <v>0.007202901020077243</v>
+        <v>0.007260354903230857</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO434" t="inlineStr">
@@ -65386,11 +65386,11 @@
         <v>0</v>
       </c>
       <c r="R440" t="n">
-        <v>0.01645368566350978</v>
+        <v>0.01658492835738029</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO440" t="inlineStr">
@@ -66419,11 +66419,11 @@
         <v>5</v>
       </c>
       <c r="R447" t="n">
-        <v>0.03813300540040893</v>
+        <v>0.03843717301710454</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO447" t="inlineStr">
@@ -67304,11 +67304,11 @@
         <v>6</v>
       </c>
       <c r="R453" t="n">
-        <v>0.04357048950380058</v>
+        <v>0.04391802916954352</v>
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO453" t="inlineStr">

--- a/diseases/d018/2020-2025.xlsx
+++ b/diseases/d018/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1809,6 +1819,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1954,6 +1969,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2694,6 +2714,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2839,6 +2864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3579,6 +3609,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3724,6 +3759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4464,6 +4504,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4757,6 +4802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5497,6 +5547,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5642,6 +5697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6382,6 +6442,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6527,6 +6592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7415,6 +7485,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7560,6 +7635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8300,6 +8380,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8445,6 +8530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9185,6 +9275,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9330,6 +9425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10218,6 +10318,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10363,6 +10468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11103,6 +11213,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11248,6 +11363,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11988,6 +12108,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12281,6 +12406,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13021,6 +13151,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13166,6 +13301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13906,6 +14046,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14051,6 +14196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14791,6 +14941,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14936,6 +15091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15824,6 +15984,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15969,6 +16134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16709,6 +16879,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16854,6 +17029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17594,6 +17774,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17739,6 +17924,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18627,6 +18817,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18772,6 +18967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19512,6 +19712,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19657,6 +19862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20397,6 +20607,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20690,6 +20905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21430,6 +21650,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21575,6 +21800,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22315,6 +22545,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22460,6 +22695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23348,6 +23588,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23493,6 +23738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24233,6 +24483,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24378,6 +24633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25118,6 +25378,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25263,6 +25528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26003,6 +26273,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26296,6 +26571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27036,6 +27316,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27181,6 +27466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27921,6 +28211,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28066,6 +28361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28806,6 +29106,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29099,6 +29404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29839,6 +30149,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29984,6 +30299,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30724,6 +31044,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30869,6 +31194,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31757,6 +32087,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31902,6 +32237,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32642,6 +32982,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32787,6 +33132,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33527,6 +33877,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33672,6 +34027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34560,6 +34920,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34705,6 +35070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35445,6 +35815,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35590,6 +35965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36330,6 +36710,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36475,6 +36860,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37363,6 +37753,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37508,6 +37903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38248,6 +38648,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38393,6 +38798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39133,6 +39543,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39278,6 +39693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40166,6 +40586,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40311,6 +40736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41051,6 +41481,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41196,6 +41631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41936,6 +42376,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42229,6 +42674,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42969,6 +43419,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43114,6 +43569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43854,6 +44314,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43999,6 +44464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44739,6 +45209,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45032,6 +45507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45772,6 +46252,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45917,6 +46402,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46657,6 +47147,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46802,6 +47297,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47542,6 +48042,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47835,6 +48340,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48575,6 +49085,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48720,6 +49235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49460,6 +49980,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49605,6 +50130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50493,6 +51023,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50638,6 +51173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51378,6 +51918,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51523,6 +52068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52263,6 +52813,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52408,6 +52963,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53296,6 +53856,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53441,6 +54006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54181,6 +54751,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54326,6 +54901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55066,6 +55646,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55359,6 +55944,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56099,6 +56689,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56244,6 +56839,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56984,6 +57584,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57129,6 +57734,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58017,6 +58627,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58162,6 +58777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58902,6 +59522,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59047,6 +59672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59787,6 +60417,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO402" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59932,6 +60567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60672,6 +61312,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60817,6 +61462,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61705,6 +62355,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61850,6 +62505,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62590,6 +63250,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62735,6 +63400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63475,6 +64145,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63768,6 +64443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64508,6 +65188,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64653,6 +65338,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65393,6 +66083,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65538,6 +66233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66426,6 +67126,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66571,6 +67276,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67311,6 +68021,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67454,6 +68169,11 @@
       <c r="S454" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO454" t="inlineStr">
